--- a/Data/results_gdf.xlsx
+++ b/Data/results_gdf.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ec7ab0b1e9f2373/Culture/0-UNI/2025-26_Boolean/Data Analytics/6_Final project/1_Final_project_boolean/Data/"/>
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3" documentId="11_CAB0919C5DAAD2BE676B6F637BADDDAEFB99A885" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C823533-62C6-43FA-A754-473F14C91608}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2004" yWindow="2256" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -138,6 +138,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -165,20 +179,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{67E56B35-8A32-4E9F-B9AF-25A5521D3C46}" name="Table1" displayName="Table1" ref="A1:R2" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{67E56B35-8A32-4E9F-B9AF-25A5521D3C46}" name="Table1" displayName="Table1" ref="A1:R2" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:R2" xr:uid="{67E56B35-8A32-4E9F-B9AF-25A5521D3C46}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{A9B8AE60-99CB-4CE2-82A1-29202426532B}" name="mu_diff_trimester_centroid"/>
@@ -504,6 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
